--- a/经济性分析测试模板（不含蒸汽）.xlsx
+++ b/经济性分析测试模板（不含蒸汽）.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" activeTab="1"/>
+    <workbookView windowWidth="24750" windowHeight="11630"/>
   </bookViews>
   <sheets>
-    <sheet name="demand" sheetId="1" r:id="rId1"/>
-    <sheet name="chillers" sheetId="2" r:id="rId2"/>
-    <sheet name="icing" sheetId="3" r:id="rId3"/>
+    <sheet name="负荷" sheetId="1" r:id="rId1"/>
+    <sheet name="电制冷机" sheetId="2" r:id="rId2"/>
+    <sheet name="蓄冰机" sheetId="3" r:id="rId3"/>
+    <sheet name="电价" sheetId="4" r:id="rId4"/>
+    <sheet name="参数" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,21 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>时间</t>
-  </si>
-  <si>
-    <t>需冷量kw</t>
-  </si>
-  <si>
-    <t>电价</t>
-  </si>
-  <si>
-    <t>冷机</t>
-  </si>
-  <si>
-    <t>设计冷量kw</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+  <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>load_kwc</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Qmax</t>
   </si>
   <si>
     <t>COP_100</t>
@@ -58,31 +57,61 @@
     <t>COP_25</t>
   </si>
   <si>
-    <t>电制冷机1</t>
-  </si>
-  <si>
-    <t>电制冷机2</t>
-  </si>
-  <si>
-    <t>电制冷机3</t>
-  </si>
-  <si>
-    <t>电制冷机4</t>
-  </si>
-  <si>
-    <t>蓄冰机</t>
-  </si>
-  <si>
-    <t>额定制冷量kw</t>
-  </si>
-  <si>
-    <t>额定消耗功率kw</t>
+    <t>中心站电制冷机1</t>
+  </si>
+  <si>
+    <t>中心站电制冷机2</t>
+  </si>
+  <si>
+    <t>2站电制冷机1</t>
+  </si>
+  <si>
+    <t>2站电制冷机2</t>
+  </si>
+  <si>
+    <t>3站电制冷机1</t>
+  </si>
+  <si>
+    <t>Q_charge_max</t>
+  </si>
+  <si>
+    <t>P_charge_max</t>
   </si>
   <si>
     <t>COP</t>
   </si>
   <si>
-    <t>蓄冷机1</t>
+    <t>E_ice_max</t>
+  </si>
+  <si>
+    <t>discharge_ratio</t>
+  </si>
+  <si>
+    <t>中心站蓄冷机1</t>
+  </si>
+  <si>
+    <t>2站蓄冷机1</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>pf</t>
+  </si>
+  <si>
+    <t>demand_price</t>
+  </si>
+  <si>
+    <t>days_in_month</t>
+  </si>
+  <si>
+    <t>p_base</t>
   </si>
 </sst>
 </file>
@@ -94,13 +123,44 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="h:mm;@"/>
-    <numFmt numFmtId="179" formatCode="0.0000_ "/>
+    <numFmt numFmtId="178" formatCode="0.0000_ "/>
+    <numFmt numFmtId="179" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -117,20 +177,8 @@
       <charset val="0"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -614,64 +662,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -680,10 +728,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,10 +740,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -704,10 +752,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,10 +764,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,10 +776,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -740,48 +788,72 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1317,329 +1389,279 @@
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.09090909090909" style="5" customWidth="1"/>
-    <col min="2" max="2" width="10.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="9.09090909090909" style="17" customWidth="1"/>
+    <col min="2" max="2" width="14.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:9">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="17" customHeight="1" spans="1:9">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" ht="15" spans="1:9">
+      <c r="A2" s="6">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19">
+        <v>2898.81</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" ht="15" spans="1:9">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="19">
+        <v>2518.27</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" ht="15" spans="1:9">
+      <c r="A4" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" ht="15" spans="1:9">
-      <c r="A2" s="8">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9">
-        <v>6759.02</v>
-      </c>
-      <c r="C2" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" ht="15" spans="1:9">
-      <c r="A3" s="11">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="B3" s="9">
-        <v>6833.49</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" ht="15" spans="1:9">
-      <c r="A4" s="8">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="B4" s="9">
-        <v>6756.07</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="B4" s="19">
+        <v>2480.04</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" ht="15" spans="1:9">
-      <c r="A5" s="11">
-        <v>0.125</v>
-      </c>
-      <c r="B5" s="9">
-        <v>6761.13</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="19">
+        <v>2459.98</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
     </row>
     <row r="6" ht="15" spans="1:9">
       <c r="A6" s="8">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="B6" s="9">
-        <v>6735.04</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="19">
+        <v>2497.93</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" ht="15" spans="1:9">
-      <c r="A7" s="11">
-        <v>0.208333333333333</v>
-      </c>
-      <c r="B7" s="9">
-        <v>6782.21</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="19">
+        <v>2416.33</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" ht="15" spans="1:9">
-      <c r="A8" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="B8" s="9">
-        <v>6736.83</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="19">
+        <v>2844.81</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" ht="15" spans="1:9">
-      <c r="A9" s="11">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="B9" s="9">
-        <v>6907.68</v>
-      </c>
-      <c r="C9" s="10">
-        <v>0.2203</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19">
+        <v>2926.12</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" ht="15" spans="1:9">
-      <c r="A10" s="8">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="B10" s="9">
-        <v>7278.19</v>
-      </c>
-      <c r="C10" s="10">
-        <v>0.9564</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="19">
+        <v>4298.46</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" ht="15" spans="1:9">
-      <c r="A11" s="11">
-        <v>0.375</v>
-      </c>
-      <c r="B11" s="9">
-        <v>8062.28</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1.1477</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="19">
+        <v>6215.85</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" ht="15" spans="1:9">
       <c r="A12" s="8">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="B12" s="9">
-        <v>8739.6</v>
-      </c>
-      <c r="C12" s="10">
-        <v>1.1477</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" s="19">
+        <v>6730.65</v>
+      </c>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" ht="15" spans="1:9">
-      <c r="A13" s="11">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="B13" s="9">
-        <v>8618.55</v>
-      </c>
-      <c r="C13" s="10">
-        <v>0.2203</v>
-      </c>
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="19">
+        <v>7007.16</v>
+      </c>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" ht="15" spans="1:9">
-      <c r="A14" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="B14" s="9">
-        <v>8602.05</v>
-      </c>
-      <c r="C14" s="10">
-        <v>0.2203</v>
-      </c>
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19">
+        <v>6231.74</v>
+      </c>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" ht="15" spans="1:9">
-      <c r="A15" s="11">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="B15" s="9">
-        <v>8499.88</v>
-      </c>
-      <c r="C15" s="10">
-        <v>0.5796</v>
-      </c>
+      <c r="A15" s="8">
+        <v>13</v>
+      </c>
+      <c r="B15" s="19">
+        <v>7020.89</v>
+      </c>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" ht="15" spans="1:9">
-      <c r="A16" s="8">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="B16" s="9">
-        <v>8447.85</v>
-      </c>
-      <c r="C16" s="10">
-        <v>0.5796</v>
-      </c>
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="19">
+        <v>7610.25</v>
+      </c>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" ht="15" spans="1:3">
-      <c r="A17" s="11">
-        <v>0.625</v>
-      </c>
-      <c r="B17" s="9">
-        <v>7561.75</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1.1477</v>
-      </c>
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="19">
+        <v>7548.67</v>
+      </c>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" ht="15" spans="1:3">
       <c r="A18" s="8">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="B18" s="9">
-        <v>7335.91</v>
-      </c>
-      <c r="C18" s="10">
-        <v>1.1477</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B18" s="19">
+        <v>6875.33</v>
+      </c>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" ht="15" spans="1:3">
-      <c r="A19" s="11">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="B19" s="9">
-        <v>7369.5</v>
-      </c>
-      <c r="C19" s="10">
-        <v>0.9564</v>
-      </c>
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="19">
+        <v>6269.62</v>
+      </c>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" ht="15" spans="1:3">
-      <c r="A20" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="B20" s="9">
-        <v>7425.73</v>
-      </c>
-      <c r="C20" s="10">
-        <v>0.9564</v>
-      </c>
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="19">
+        <v>4943.39</v>
+      </c>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" ht="15" spans="1:3">
-      <c r="A21" s="11">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="B21" s="9">
-        <v>7146.04</v>
-      </c>
-      <c r="C21" s="10">
-        <v>0.9564</v>
-      </c>
+      <c r="A21" s="8">
+        <v>19</v>
+      </c>
+      <c r="B21" s="19">
+        <v>4309.44</v>
+      </c>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" ht="15" spans="1:3">
-      <c r="A22" s="8">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="B22" s="9">
-        <v>7373.37</v>
-      </c>
-      <c r="C22" s="10">
-        <v>0.9564</v>
-      </c>
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="19">
+        <v>3982.52</v>
+      </c>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" ht="15" spans="1:3">
-      <c r="A23" s="11">
-        <v>0.875</v>
-      </c>
-      <c r="B23" s="9">
-        <v>7078.45</v>
-      </c>
-      <c r="C23" s="10">
-        <v>0.9564</v>
-      </c>
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="19">
+        <v>3380.74</v>
+      </c>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" ht="15" spans="1:3">
       <c r="A24" s="8">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="B24" s="9">
-        <v>7373.73</v>
-      </c>
-      <c r="C24" s="10">
-        <v>0.9564</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B24" s="19">
+        <v>3768.18</v>
+      </c>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" ht="15" spans="1:3">
-      <c r="A25" s="11">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="B25" s="9">
-        <v>7136.02</v>
-      </c>
-      <c r="C25" s="10">
-        <v>0.5796</v>
-      </c>
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="19">
+        <v>3048.4</v>
+      </c>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" ht="15" spans="1:3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1650,111 +1672,131 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="15.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="13.4545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="14">
+        <v>7032</v>
+      </c>
+      <c r="C2" s="14">
+        <v>5.599</v>
+      </c>
+      <c r="D2" s="14">
+        <v>5.583</v>
+      </c>
+      <c r="E2" s="14">
+        <v>5.167</v>
+      </c>
+      <c r="F2" s="14">
+        <v>4.388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
-        <v>7032</v>
-      </c>
-      <c r="C2" s="3">
-        <v>5.599</v>
-      </c>
-      <c r="D2" s="3">
-        <v>5.583</v>
-      </c>
-      <c r="E2" s="3">
-        <v>5.167</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4.388</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="14">
+        <v>3516</v>
+      </c>
+      <c r="C3" s="14">
+        <v>5.39</v>
+      </c>
+      <c r="D3" s="14">
+        <v>5.76</v>
+      </c>
+      <c r="E3" s="14">
+        <v>5.543</v>
+      </c>
+      <c r="F3" s="14">
+        <v>4.695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B4" s="14">
+        <v>3517</v>
+      </c>
+      <c r="C4" s="14">
+        <v>6.26</v>
+      </c>
+      <c r="D4" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="E4" s="14">
+        <v>7.52</v>
+      </c>
+      <c r="F4" s="14">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14">
+        <v>2210</v>
+      </c>
+      <c r="C5" s="14">
+        <v>6.02</v>
+      </c>
+      <c r="D5" s="14">
+        <v>5.58</v>
+      </c>
+      <c r="E5" s="14">
+        <v>4.72</v>
+      </c>
+      <c r="F5" s="14">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16">
         <v>3516</v>
       </c>
-      <c r="C3" s="3">
-        <v>5.39</v>
-      </c>
-      <c r="D3" s="3">
-        <v>5.76</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5.543</v>
-      </c>
-      <c r="F3" s="3">
-        <v>4.695</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2">
-        <v>3517</v>
-      </c>
-      <c r="C4" s="3">
-        <v>6.26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7.43</v>
-      </c>
-      <c r="E4" s="3">
-        <v>7.52</v>
-      </c>
-      <c r="F4" s="3">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
-        <v>2210</v>
-      </c>
-      <c r="C5" s="3">
-        <v>6.02</v>
-      </c>
-      <c r="D5" s="3">
-        <v>5.58</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4.72</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3.33</v>
+      <c r="C6" s="14">
+        <v>6.255</v>
+      </c>
+      <c r="D6" s="14">
+        <v>8.59</v>
+      </c>
+      <c r="E6" s="14">
+        <v>12.37</v>
+      </c>
+      <c r="F6" s="14">
+        <v>10.83</v>
       </c>
     </row>
   </sheetData>
@@ -1766,39 +1808,344 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
+    <col min="1" max="1" width="15.3636363636364" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="12.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="16.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" ht="15" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="F1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2">
+    </row>
+    <row r="2" ht="15" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3">
         <v>5016</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>1182</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>4.24</v>
+      </c>
+      <c r="E2" s="3">
+        <v>49238</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2330</v>
+      </c>
+      <c r="C3" s="3">
+        <v>531</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4.39</v>
+      </c>
+      <c r="E3" s="3">
+        <v>24619</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" ht="15" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:2">
+      <c r="A2" s="6">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:2">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:2">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:2">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:2">
+      <c r="A6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:2">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:2">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:2">
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:2">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:2">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1.1477</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:2">
+      <c r="A12" s="8">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1.1477</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:2">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:2">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7">
+        <v>0.2203</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:2">
+      <c r="A15" s="8">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.5796</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:2">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7">
+        <v>0.5796</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:2">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7">
+        <v>1.1477</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:2">
+      <c r="A18" s="8">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1.1477</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:2">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:2">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:2">
+      <c r="A21" s="8">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="1:2">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="23" ht="15" spans="1:2">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:2">
+      <c r="A24" s="8">
+        <v>22</v>
+      </c>
+      <c r="B24" s="7">
+        <v>0.9564</v>
+      </c>
+    </row>
+    <row r="25" ht="15" spans="1:2">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="7">
+        <v>0.5796</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="13.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
